--- a/addon/design/revenuesheet-dashboard-template.xlsx
+++ b/addon/design/revenuesheet-dashboard-template.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subscriptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refunds" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MRR monthly" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cohorts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subscriptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refunds" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MRR monthly" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="rs_orders">Orders!$A$1:$G$61</definedName>
@@ -41,7 +42,7 @@
     <numFmt numFmtId="173" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="174" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,8 +121,13 @@
       <color rgb="000A7A55"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="JetBrains Mono"/>
+      <color rgb="005C5C5C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -131,6 +137,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -201,27 +227,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00E6E6E6"/>
-      </left>
-      <top style="medium">
-        <color rgb="00B42318"/>
-      </top>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="00B42318"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00E6E6E6"/>
-      </right>
-      <top style="medium">
-        <color rgb="00B42318"/>
-      </top>
-    </border>
-    <border>
       <bottom style="thin">
         <color rgb="008C8C8C"/>
       </bottom>
@@ -264,11 +269,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="000D0D0D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008C8C8C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E6E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E6E6E6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -290,11 +331,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -320,17 +356,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -344,30 +380,63 @@
     <xf numFmtId="171" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -391,24 +460,54 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="000A7A55"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E7F3EE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
         <color rgb="00B42318"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="005C5C5C"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBEAE8"/>
+          <fgColor rgb="00CCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E6E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -655,7 +754,7 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
               <a:solidFill>
-                <a:srgbClr val="B42318"/>
+                <a:srgbClr val="0D0D0D"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -665,11 +764,11 @@
             <size val="4"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B42318"/>
+                <a:srgbClr val="0D0D0D"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:solidFill>
-                  <a:srgbClr val="B42318"/>
+                  <a:srgbClr val="0D0D0D"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1141,7 +1240,7 @@
     <row r="2" ht="21" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ● SYNCED 2026-10-09 10:02 · LEMON SQUEEZY, POLAR, GUMROAD · HOURLY</t>
+          <t xml:space="preserve">   ● SYNCED 2026-10-09 10:02 · STRIPE, LEMON SQUEEZY, POLAR, GUMROAD, CSV · HOURLY</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -1157,7 +1256,7 @@
       <c r="L2" s="5" t="n"/>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXAMPLE DATA — NOT REAL CUSTOMERS  </t>
+          <t xml:space="preserve">EXAMPLE DATA · NOT REAL CUSTOMERS  </t>
         </is>
       </c>
       <c r="N2" s="5" t="n"/>
@@ -1210,70 +1309,71 @@
       <c r="K4" s="9" t="n"/>
       <c r="L4" s="10" t="n"/>
       <c r="M4" s="7" t="n"/>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>CHURN · 30D</t>
         </is>
       </c>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="13" t="n"/>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="10" t="n"/>
       <c r="Q4" s="7" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="n"/>
-      <c r="B5" s="14">
+      <c r="B5" s="11">
         <f>'MRR monthly'!E13</f>
         <v/>
       </c>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="16" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="13" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="11" t="n">
         <v>6912</v>
       </c>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="16" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="13" t="n"/>
       <c r="I5" s="7" t="n"/>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="14" t="n">
         <v>418</v>
       </c>
-      <c r="K5" s="15" t="n"/>
-      <c r="L5" s="16" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="13" t="n"/>
       <c r="M5" s="7" t="n"/>
-      <c r="N5" s="18">
+      <c r="N5" s="15">
         <f>'MRR monthly'!F13</f>
         <v/>
       </c>
-      <c r="O5" s="15" t="n"/>
-      <c r="P5" s="16" t="n"/>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="13" t="n"/>
       <c r="Q5" s="7" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="7" t="n"/>
-      <c r="B6" s="19">
+      <c r="B6" s="16">
         <f>'MRR monthly'!E13/'MRR monthly'!E12-1</f>
         <v/>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="21" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="18" t="n"/>
       <c r="E6" s="7" t="n"/>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="16" t="n">
         <v>0.051</v>
       </c>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="21" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="18" t="n"/>
       <c r="I6" s="7" t="n"/>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="21" t="n"/>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="18" t="n"/>
       <c r="M6" s="7" t="n"/>
-      <c r="N6" s="23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O6" s="20" t="n"/>
-      <c r="P6" s="21" t="n"/>
+      <c r="N6" s="20">
+        <f>('MRR monthly'!F13-'MRR monthly'!F12)*100</f>
+        <v/>
+      </c>
+      <c r="O6" s="17" t="n"/>
+      <c r="P6" s="18" t="n"/>
       <c r="Q6" s="7" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1297,13 +1397,13 @@
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="7" t="n"/>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>MRR by source · last 12 months</t>
         </is>
       </c>
       <c r="M8" s="7" t="n"/>
-      <c r="N8" s="24" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t>Churn · monthly</t>
         </is>
@@ -1597,13 +1697,13 @@
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Revenue by product · 30d</t>
         </is>
       </c>
       <c r="I24" s="7" t="n"/>
-      <c r="J24" s="24" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>Revenue by source · 30d</t>
         </is>
@@ -1612,51 +1712,51 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="n"/>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>PRODUCT</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="H25" s="27" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>VS PRIOR</t>
         </is>
       </c>
       <c r="I25" s="7" t="n"/>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J25" s="25" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
-      <c r="K25" s="29" t="n"/>
-      <c r="L25" s="27" t="inlineStr">
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="24" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="M25" s="26" t="n"/>
-      <c r="N25" s="27" t="inlineStr">
+      <c r="M25" s="23" t="n"/>
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>SHARE</t>
         </is>
       </c>
-      <c r="O25" s="27" t="inlineStr">
+      <c r="O25" s="24" t="inlineStr">
         <is>
           <t>VS PRIOR</t>
         </is>
       </c>
-      <c r="P25" s="25" t="inlineStr">
+      <c r="P25" s="22" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
@@ -1665,41 +1765,41 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="n"/>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>Demo SaaS · Pro</t>
         </is>
       </c>
-      <c r="D26" s="31" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>Polar</t>
         </is>
       </c>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="33" t="n">
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n">
         <v>2140</v>
       </c>
-      <c r="H26" s="34" t="n">
+      <c r="H26" s="31" t="n">
         <v>0.124</v>
       </c>
       <c r="I26" s="7" t="n"/>
-      <c r="J26" s="35" t="inlineStr">
+      <c r="J26" s="32" t="inlineStr">
         <is>
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="K26" s="36" t="n"/>
-      <c r="L26" s="33" t="n">
+      <c r="K26" s="33" t="n"/>
+      <c r="L26" s="30" t="n">
         <v>2080</v>
       </c>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="37" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="O26" s="34" t="n">
+      <c r="M26" s="29" t="n"/>
+      <c r="N26" s="34" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="O26" s="31" t="n">
         <v>0.042</v>
       </c>
-      <c r="P26" s="38" t="inlineStr">
+      <c r="P26" s="35" t="inlineStr">
         <is>
           <t>● Synced</t>
         </is>
@@ -1708,41 +1808,41 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="n"/>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>Example Course Bundle</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="D27" s="28" t="inlineStr">
         <is>
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="33" t="n">
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n">
         <v>1890</v>
       </c>
-      <c r="H27" s="34" t="n">
+      <c r="H27" s="31" t="n">
         <v>0.062</v>
       </c>
       <c r="I27" s="7" t="n"/>
-      <c r="J27" s="35" t="inlineStr">
+      <c r="J27" s="32" t="inlineStr">
         <is>
           <t>Polar</t>
         </is>
       </c>
-      <c r="K27" s="36" t="n"/>
-      <c r="L27" s="33" t="n">
+      <c r="K27" s="33" t="n"/>
+      <c r="L27" s="30" t="n">
         <v>3460</v>
       </c>
-      <c r="M27" s="32" t="n"/>
-      <c r="N27" s="37" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="O27" s="34" t="n">
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="34" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="O27" s="31" t="n">
         <v>0.149</v>
       </c>
-      <c r="P27" s="38" t="inlineStr">
+      <c r="P27" s="35" t="inlineStr">
         <is>
           <t>● Synced</t>
         </is>
@@ -1751,41 +1851,41 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="n"/>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Demo SaaS · Team</t>
         </is>
       </c>
-      <c r="D28" s="31" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>Polar</t>
         </is>
       </c>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="33" t="n">
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n">
         <v>1320</v>
       </c>
-      <c r="H28" s="34" t="n">
+      <c r="H28" s="31" t="n">
         <v>0.18</v>
       </c>
       <c r="I28" s="7" t="n"/>
-      <c r="J28" s="35" t="inlineStr">
+      <c r="J28" s="32" t="inlineStr">
         <is>
           <t>Gumroad</t>
         </is>
       </c>
-      <c r="K28" s="36" t="n"/>
-      <c r="L28" s="33" t="n">
+      <c r="K28" s="33" t="n"/>
+      <c r="L28" s="30" t="n">
         <v>1372</v>
       </c>
-      <c r="M28" s="32" t="n"/>
-      <c r="N28" s="37" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="O28" s="34" t="n">
+      <c r="M28" s="29" t="n"/>
+      <c r="N28" s="34" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="O28" s="31" t="n">
         <v>-0.048</v>
       </c>
-      <c r="P28" s="38" t="inlineStr">
+      <c r="P28" s="35" t="inlineStr">
         <is>
           <t>● Synced</t>
         </is>
@@ -1794,50 +1894,64 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="n"/>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Template Kit (example)</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Gumroad</t>
         </is>
       </c>
-      <c r="E29" s="32" t="n"/>
-      <c r="F29" s="33" t="n">
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n">
         <v>860</v>
       </c>
-      <c r="H29" s="34" t="n">
+      <c r="H29" s="31" t="n">
         <v>-0.031</v>
       </c>
       <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
+      <c r="J29" s="32" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="K29" s="33" t="n"/>
+      <c r="L29" s="30" t="n">
+        <v>846</v>
+      </c>
+      <c r="M29" s="29" t="n"/>
+      <c r="N29" s="34" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="O29" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="35" t="inlineStr">
+        <is>
+          <t>● Synced</t>
+        </is>
+      </c>
       <c r="Q29" s="7" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="n"/>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Sample Icon Pack</t>
         </is>
       </c>
-      <c r="D30" s="31" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>Gumroad</t>
         </is>
       </c>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="33" t="n">
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n">
         <v>512</v>
       </c>
-      <c r="H30" s="34" t="n">
+      <c r="H30" s="31" t="n">
         <v>-0.08599999999999999</v>
       </c>
       <c r="I30" s="7" t="n"/>
@@ -1852,21 +1966,21 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="n"/>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Sample E-book</t>
         </is>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="33" t="n">
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n">
         <v>190</v>
       </c>
-      <c r="H31" s="34" t="n">
+      <c r="H31" s="31" t="n">
         <v>0.02</v>
       </c>
       <c r="I31" s="7" t="n"/>
@@ -1881,18 +1995,18 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="n"/>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D32" s="40" t="inlineStr"/>
-      <c r="E32" s="32" t="n"/>
-      <c r="F32" s="41">
+      <c r="D32" s="37" t="inlineStr"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="38">
         <f>SUM(F26:F31)</f>
         <v/>
       </c>
-      <c r="H32" s="42" t="n">
+      <c r="H32" s="39" t="n">
         <v>0.051</v>
       </c>
       <c r="I32" s="7" t="n"/>
@@ -1945,7 +2059,7 @@
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="7" t="n"/>
-      <c r="B35" s="43" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>Managed by RevenueSheet · edits in synced ranges are overwritten · add your own columns to the right of P · example data</t>
         </is>
@@ -1953,9 +2067,10 @@
       <c r="Q35" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J29:K29"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F25:G25"/>
@@ -2003,44 +2118,62 @@
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N6">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="1">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="0">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H32">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O26:O28">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+  <conditionalFormatting sqref="O26:O29">
+    <cfRule type="cellIs" priority="16" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="17" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2052,6 +2185,297 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000D0D0D"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.71" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="7.29" customWidth="1" min="3" max="3"/>
+    <col width="9.57" customWidth="1" min="4" max="4"/>
+    <col width="9.57" customWidth="1" min="5" max="5"/>
+    <col width="9.57" customWidth="1" min="6" max="6"/>
+    <col width="9.57" customWidth="1" min="7" max="7"/>
+    <col width="9.57" customWidth="1" min="8" max="8"/>
+    <col width="9.57" customWidth="1" min="9" max="9"/>
+    <col width="2.71" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Cohort retention</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="B2" s="41" t="inlineStr">
+        <is>
+          <t>LOGO RETENTION BY START MONTH · DARKER CELL = HIGHER RETENTION · EXAMPLE DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="42" t="inlineStr">
+        <is>
+          <t>COHORT</t>
+        </is>
+      </c>
+      <c r="C4" s="43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="F4" s="43" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="G4" s="43" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="H4" s="43" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="I4" s="43" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="44" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="n">
+        <v>38</v>
+      </c>
+      <c r="D5" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="46" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F5" s="46" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H5" s="46" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F6" s="46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" s="46" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>42</v>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H7" s="46" t="n"/>
+      <c r="I7" s="46" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="44" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>48</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="46" t="n"/>
+      <c r="I8" s="46" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>51</v>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="46" t="n"/>
+      <c r="I9" s="46" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>29</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="46" t="n"/>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="46" t="n"/>
+      <c r="I10" s="46" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>RAMP</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>&lt;80%</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G12" s="50" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>99%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>Managed by RevenueSheet · edits in synced ranges are overwritten · example data</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:I10">
+    <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
+      <formula>AND(ISNUMBER(D5),D5&gt;=0.99)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="4" stopIfTrue="1">
+      <formula>AND(ISNUMBER(D5),D5&gt;=0.9)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="5" stopIfTrue="1">
+      <formula>AND(ISNUMBER(D5),D5&gt;=0.85)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6" stopIfTrue="1">
+      <formula>AND(ISNUMBER(D5),D5&gt;=0.8)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="7" stopIfTrue="1">
+      <formula>AND(ISNUMBER(D5),D5&lt;0.8)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000D0D0D"/>
@@ -2071,37 +2495,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="C1" s="44" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="E1" s="44" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Customer email</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Amount (USD)</t>
         </is>
       </c>
-      <c r="G1" s="44" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2113,12 +2537,12 @@
           <t>EX-10480</t>
         </is>
       </c>
-      <c r="B2" s="45" t="n">
+      <c r="B2" s="53" t="n">
         <v>46304.41666666666</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -2131,7 +2555,7 @@
           <t>customer247@example.com</t>
         </is>
       </c>
-      <c r="F2" s="46" t="n">
+      <c r="F2" s="54" t="n">
         <v>19</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -2146,12 +2570,12 @@
           <t>EX-10479</t>
         </is>
       </c>
-      <c r="B3" s="45" t="n">
+      <c r="B3" s="53" t="n">
         <v>46304.125</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -2164,7 +2588,7 @@
           <t>customer673@example.com</t>
         </is>
       </c>
-      <c r="F3" s="46" t="n">
+      <c r="F3" s="54" t="n">
         <v>9</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -2179,12 +2603,12 @@
           <t>EX-10478</t>
         </is>
       </c>
-      <c r="B4" s="45" t="n">
+      <c r="B4" s="53" t="n">
         <v>46303.83333333334</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -2194,15 +2618,15 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>customer684@example.com</t>
-        </is>
-      </c>
-      <c r="F4" s="46" t="n">
-        <v>19</v>
+          <t>customer754@example.com</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>refunded</t>
         </is>
       </c>
     </row>
@@ -2212,26 +2636,26 @@
           <t>EX-10477</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="53" t="n">
         <v>46303.54166666666</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>customer660@example.com</t>
-        </is>
-      </c>
-      <c r="F5" s="46" t="n">
-        <v>19</v>
+          <t>customer829@example.com</t>
+        </is>
+      </c>
+      <c r="F5" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -2245,30 +2669,30 @@
           <t>EX-10476</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="53" t="n">
         <v>46303.25</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>customer733@example.com</t>
-        </is>
-      </c>
-      <c r="F6" s="46" t="n">
-        <v>9</v>
+          <t>customer310@example.com</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2702,12 @@
           <t>EX-10475</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="53" t="n">
         <v>46302.95833333334</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2296,8 +2720,8 @@
           <t>customer895@example.com</t>
         </is>
       </c>
-      <c r="F7" s="46" t="n">
-        <v>49</v>
+      <c r="F7" s="54" t="n">
+        <v>12</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -2311,12 +2735,12 @@
           <t>EX-10474</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="53" t="n">
         <v>46302.66666666666</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2329,7 +2753,7 @@
           <t>customer470@example.com</t>
         </is>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="54" t="n">
         <v>49</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2344,12 +2768,12 @@
           <t>EX-10473</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="53" t="n">
         <v>46302.375</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2362,7 +2786,7 @@
           <t>customer898@example.com</t>
         </is>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="54" t="n">
         <v>19</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -2377,12 +2801,12 @@
           <t>EX-10472</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n">
+      <c r="B10" s="53" t="n">
         <v>46302.08333333334</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2395,7 +2819,7 @@
           <t>customer637@example.com</t>
         </is>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="54" t="n">
         <v>9</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -2410,12 +2834,12 @@
           <t>EX-10471</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n">
+      <c r="B11" s="53" t="n">
         <v>46301.79166666666</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2428,7 +2852,7 @@
           <t>customer723@example.com</t>
         </is>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="54" t="n">
         <v>29</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2443,7 +2867,7 @@
           <t>EX-10470</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n">
+      <c r="B12" s="53" t="n">
         <v>46301.5</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2461,7 +2885,7 @@
           <t>customer268@example.com</t>
         </is>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="54" t="n">
         <v>9</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -2476,12 +2900,12 @@
           <t>EX-10469</t>
         </is>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="53" t="n">
         <v>46301.20833333334</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2494,7 +2918,7 @@
           <t>customer140@example.com</t>
         </is>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="54" t="n">
         <v>19</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -2509,30 +2933,30 @@
           <t>EX-10468</t>
         </is>
       </c>
-      <c r="B14" s="45" t="n">
+      <c r="B14" s="53" t="n">
         <v>46300.91666666666</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>customer908@example.com</t>
-        </is>
-      </c>
-      <c r="F14" s="46" t="n">
-        <v>9</v>
+          <t>customer448@example.com</t>
+        </is>
+      </c>
+      <c r="F14" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>refunded</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2966,12 @@
           <t>EX-10467</t>
         </is>
       </c>
-      <c r="B15" s="45" t="n">
+      <c r="B15" s="53" t="n">
         <v>46300.625</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2557,11 +2981,11 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>customer608@example.com</t>
-        </is>
-      </c>
-      <c r="F15" s="46" t="n">
-        <v>29</v>
+          <t>customer916@example.com</t>
+        </is>
+      </c>
+      <c r="F15" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -2575,26 +2999,26 @@
           <t>EX-10466</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="53" t="n">
         <v>46300.33333333334</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>customer376@example.com</t>
-        </is>
-      </c>
-      <c r="F16" s="46" t="n">
-        <v>49</v>
+          <t>customer585@example.com</t>
+        </is>
+      </c>
+      <c r="F16" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -2608,26 +3032,26 @@
           <t>EX-10465</t>
         </is>
       </c>
-      <c r="B17" s="45" t="n">
+      <c r="B17" s="53" t="n">
         <v>46300.04166666666</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Sample E-book</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>customer848@example.com</t>
-        </is>
-      </c>
-      <c r="F17" s="46" t="n">
-        <v>12</v>
+          <t>customer691@example.com</t>
+        </is>
+      </c>
+      <c r="F17" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -2641,12 +3065,12 @@
           <t>EX-10464</t>
         </is>
       </c>
-      <c r="B18" s="45" t="n">
+      <c r="B18" s="53" t="n">
         <v>46299.75</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2656,15 +3080,15 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>customer941@example.com</t>
-        </is>
-      </c>
-      <c r="F18" s="46" t="n">
+          <t>customer455@example.com</t>
+        </is>
+      </c>
+      <c r="F18" s="54" t="n">
         <v>29</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -2674,26 +3098,26 @@
           <t>EX-10463</t>
         </is>
       </c>
-      <c r="B19" s="45" t="n">
+      <c r="B19" s="53" t="n">
         <v>46299.45833333334</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Sample Icon Pack</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>customer455@example.com</t>
-        </is>
-      </c>
-      <c r="F19" s="46" t="n">
-        <v>29</v>
+          <t>customer725@example.com</t>
+        </is>
+      </c>
+      <c r="F19" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -2707,7 +3131,7 @@
           <t>EX-10462</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n">
+      <c r="B20" s="53" t="n">
         <v>46299.16666666666</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -2722,10 +3146,10 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>customer725@example.com</t>
-        </is>
-      </c>
-      <c r="F20" s="46" t="n">
+          <t>customer886@example.com</t>
+        </is>
+      </c>
+      <c r="F20" s="54" t="n">
         <v>49</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -2740,26 +3164,26 @@
           <t>EX-10461</t>
         </is>
       </c>
-      <c r="B21" s="45" t="n">
+      <c r="B21" s="53" t="n">
         <v>46298.875</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Sample Icon Pack</t>
+          <t>Template Kit (example)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>customer886@example.com</t>
-        </is>
-      </c>
-      <c r="F21" s="46" t="n">
-        <v>49</v>
+          <t>customer500@example.com</t>
+        </is>
+      </c>
+      <c r="F21" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -2773,12 +3197,12 @@
           <t>EX-10460</t>
         </is>
       </c>
-      <c r="B22" s="45" t="n">
+      <c r="B22" s="53" t="n">
         <v>46298.58333333334</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -2788,11 +3212,11 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>customer500@example.com</t>
-        </is>
-      </c>
-      <c r="F22" s="46" t="n">
-        <v>19</v>
+          <t>customer511@example.com</t>
+        </is>
+      </c>
+      <c r="F22" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -2806,12 +3230,12 @@
           <t>EX-10459</t>
         </is>
       </c>
-      <c r="B23" s="45" t="n">
+      <c r="B23" s="53" t="n">
         <v>46298.29166666666</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -2821,11 +3245,11 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>customer511@example.com</t>
-        </is>
-      </c>
-      <c r="F23" s="46" t="n">
-        <v>9</v>
+          <t>customer984@example.com</t>
+        </is>
+      </c>
+      <c r="F23" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -2839,25 +3263,25 @@
           <t>EX-10458</t>
         </is>
       </c>
-      <c r="B24" s="45" t="n">
+      <c r="B24" s="53" t="n">
         <v>46298</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Template Kit (example)</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>customer984@example.com</t>
-        </is>
-      </c>
-      <c r="F24" s="46" t="n">
+          <t>customer799@example.com</t>
+        </is>
+      </c>
+      <c r="F24" s="54" t="n">
         <v>29</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2872,26 +3296,26 @@
           <t>EX-10457</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n">
+      <c r="B25" s="53" t="n">
         <v>46297.70833333334</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>customer799@example.com</t>
-        </is>
-      </c>
-      <c r="F25" s="46" t="n">
-        <v>29</v>
+          <t>customer280@example.com</t>
+        </is>
+      </c>
+      <c r="F25" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
@@ -2905,7 +3329,7 @@
           <t>EX-10456</t>
         </is>
       </c>
-      <c r="B26" s="45" t="n">
+      <c r="B26" s="53" t="n">
         <v>46297.41666666666</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -2920,10 +3344,10 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>customer280@example.com</t>
-        </is>
-      </c>
-      <c r="F26" s="46" t="n">
+          <t>customer596@example.com</t>
+        </is>
+      </c>
+      <c r="F26" s="54" t="n">
         <v>19</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -2938,25 +3362,25 @@
           <t>EX-10455</t>
         </is>
       </c>
-      <c r="B27" s="45" t="n">
+      <c r="B27" s="53" t="n">
         <v>46297.125</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>customer596@example.com</t>
-        </is>
-      </c>
-      <c r="F27" s="46" t="n">
+          <t>customer104@example.com</t>
+        </is>
+      </c>
+      <c r="F27" s="54" t="n">
         <v>19</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -2971,12 +3395,12 @@
           <t>EX-10454</t>
         </is>
       </c>
-      <c r="B28" s="45" t="n">
+      <c r="B28" s="53" t="n">
         <v>46296.83333333334</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -2986,11 +3410,11 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>customer104@example.com</t>
-        </is>
-      </c>
-      <c r="F28" s="46" t="n">
-        <v>19</v>
+          <t>customer724@example.com</t>
+        </is>
+      </c>
+      <c r="F28" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -3004,26 +3428,26 @@
           <t>EX-10453</t>
         </is>
       </c>
-      <c r="B29" s="45" t="n">
+      <c r="B29" s="53" t="n">
         <v>46296.54166666666</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Sample E-book</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>customer724@example.com</t>
-        </is>
-      </c>
-      <c r="F29" s="46" t="n">
-        <v>49</v>
+          <t>customer979@example.com</t>
+        </is>
+      </c>
+      <c r="F29" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
@@ -3037,26 +3461,26 @@
           <t>EX-10452</t>
         </is>
       </c>
-      <c r="B30" s="45" t="n">
+      <c r="B30" s="53" t="n">
         <v>46296.25</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Template Kit (example)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>customer979@example.com</t>
-        </is>
-      </c>
-      <c r="F30" s="46" t="n">
-        <v>29</v>
+          <t>customer991@example.com</t>
+        </is>
+      </c>
+      <c r="F30" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -3070,12 +3494,12 @@
           <t>EX-10451</t>
         </is>
       </c>
-      <c r="B31" s="45" t="n">
+      <c r="B31" s="53" t="n">
         <v>46295.95833333334</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3085,11 +3509,11 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>customer991@example.com</t>
-        </is>
-      </c>
-      <c r="F31" s="46" t="n">
-        <v>79</v>
+          <t>customer503@example.com</t>
+        </is>
+      </c>
+      <c r="F31" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
@@ -3103,26 +3527,26 @@
           <t>EX-10450</t>
         </is>
       </c>
-      <c r="B32" s="45" t="n">
+      <c r="B32" s="53" t="n">
         <v>46295.66666666666</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Template Kit (example)</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>customer508@example.com</t>
-        </is>
-      </c>
-      <c r="F32" s="46" t="n">
-        <v>79</v>
+          <t>customer295@example.com</t>
+        </is>
+      </c>
+      <c r="F32" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -3136,26 +3560,26 @@
           <t>EX-10449</t>
         </is>
       </c>
-      <c r="B33" s="45" t="n">
+      <c r="B33" s="53" t="n">
         <v>46295.375</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Sample Icon Pack</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>customer510@example.com</t>
-        </is>
-      </c>
-      <c r="F33" s="46" t="n">
-        <v>9</v>
+          <t>customer212@example.com</t>
+        </is>
+      </c>
+      <c r="F33" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
@@ -3169,26 +3593,26 @@
           <t>EX-10448</t>
         </is>
       </c>
-      <c r="B34" s="45" t="n">
+      <c r="B34" s="53" t="n">
         <v>46295.08333333334</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Sample Icon Pack</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>customer551@example.com</t>
-        </is>
-      </c>
-      <c r="F34" s="46" t="n">
-        <v>19</v>
+          <t>customer100@example.com</t>
+        </is>
+      </c>
+      <c r="F34" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -3202,26 +3626,26 @@
           <t>EX-10447</t>
         </is>
       </c>
-      <c r="B35" s="45" t="n">
+      <c r="B35" s="53" t="n">
         <v>46294.79166666666</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>customer153@example.com</t>
-        </is>
-      </c>
-      <c r="F35" s="46" t="n">
-        <v>9</v>
+          <t>customer472@example.com</t>
+        </is>
+      </c>
+      <c r="F35" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
@@ -3235,12 +3659,12 @@
           <t>EX-10446</t>
         </is>
       </c>
-      <c r="B36" s="45" t="n">
+      <c r="B36" s="53" t="n">
         <v>46294.5</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3250,15 +3674,15 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>customer649@example.com</t>
-        </is>
-      </c>
-      <c r="F36" s="46" t="n">
+          <t>customer728@example.com</t>
+        </is>
+      </c>
+      <c r="F36" s="54" t="n">
         <v>9</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -3268,30 +3692,30 @@
           <t>EX-10445</t>
         </is>
       </c>
-      <c r="B37" s="45" t="n">
+      <c r="B37" s="53" t="n">
         <v>46294.20833333334</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>customer172@example.com</t>
-        </is>
-      </c>
-      <c r="F37" s="46" t="n">
-        <v>29</v>
+          <t>customer716@example.com</t>
+        </is>
+      </c>
+      <c r="F37" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -3301,26 +3725,26 @@
           <t>EX-10444</t>
         </is>
       </c>
-      <c r="B38" s="45" t="n">
+      <c r="B38" s="53" t="n">
         <v>46293.91666666666</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Sample Icon Pack</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>customer749@example.com</t>
-        </is>
-      </c>
-      <c r="F38" s="46" t="n">
-        <v>79</v>
+          <t>customer969@example.com</t>
+        </is>
+      </c>
+      <c r="F38" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -3334,30 +3758,30 @@
           <t>EX-10443</t>
         </is>
       </c>
-      <c r="B39" s="45" t="n">
+      <c r="B39" s="53" t="n">
         <v>46293.625</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Template Kit (example)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>customer585@example.com</t>
-        </is>
-      </c>
-      <c r="F39" s="46" t="n">
-        <v>29</v>
+          <t>customer419@example.com</t>
+        </is>
+      </c>
+      <c r="F39" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3791,7 @@
           <t>EX-10442</t>
         </is>
       </c>
-      <c r="B40" s="45" t="n">
+      <c r="B40" s="53" t="n">
         <v>46293.33333333334</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -3377,16 +3801,16 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Template Kit (example)</t>
+          <t>Sample E-book</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>customer591@example.com</t>
-        </is>
-      </c>
-      <c r="F40" s="46" t="n">
-        <v>9</v>
+          <t>customer450@example.com</t>
+        </is>
+      </c>
+      <c r="F40" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -3400,26 +3824,26 @@
           <t>EX-10441</t>
         </is>
       </c>
-      <c r="B41" s="45" t="n">
+      <c r="B41" s="53" t="n">
         <v>46293.04166666666</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Sample Icon Pack</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>customer204@example.com</t>
-        </is>
-      </c>
-      <c r="F41" s="46" t="n">
-        <v>29</v>
+          <t>customer123@example.com</t>
+        </is>
+      </c>
+      <c r="F41" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
@@ -3433,26 +3857,26 @@
           <t>EX-10440</t>
         </is>
       </c>
-      <c r="B42" s="45" t="n">
+      <c r="B42" s="53" t="n">
         <v>46292.75</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Template Kit (example)</t>
+          <t>Sample Icon Pack</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>customer948@example.com</t>
-        </is>
-      </c>
-      <c r="F42" s="46" t="n">
-        <v>29</v>
+          <t>customer806@example.com</t>
+        </is>
+      </c>
+      <c r="F42" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -3466,26 +3890,26 @@
           <t>EX-10439</t>
         </is>
       </c>
-      <c r="B43" s="45" t="n">
+      <c r="B43" s="53" t="n">
         <v>46292.45833333334</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Example Course Bundle</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>customer310@example.com</t>
-        </is>
-      </c>
-      <c r="F43" s="46" t="n">
-        <v>19</v>
+          <t>customer758@example.com</t>
+        </is>
+      </c>
+      <c r="F43" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
@@ -3499,26 +3923,26 @@
           <t>EX-10438</t>
         </is>
       </c>
-      <c r="B44" s="45" t="n">
+      <c r="B44" s="53" t="n">
         <v>46292.16666666666</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>customer656@example.com</t>
-        </is>
-      </c>
-      <c r="F44" s="46" t="n">
-        <v>29</v>
+          <t>customer475@example.com</t>
+        </is>
+      </c>
+      <c r="F44" s="54" t="n">
+        <v>12</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -3532,26 +3956,26 @@
           <t>EX-10437</t>
         </is>
       </c>
-      <c r="B45" s="45" t="n">
+      <c r="B45" s="53" t="n">
         <v>46291.875</v>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>customer984@example.com</t>
-        </is>
-      </c>
-      <c r="F45" s="46" t="n">
-        <v>79</v>
+          <t>customer654@example.com</t>
+        </is>
+      </c>
+      <c r="F45" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
@@ -3565,12 +3989,12 @@
           <t>EX-10436</t>
         </is>
       </c>
-      <c r="B46" s="45" t="n">
+      <c r="B46" s="53" t="n">
         <v>46291.58333333334</v>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -3580,11 +4004,11 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>customer475@example.com</t>
-        </is>
-      </c>
-      <c r="F46" s="46" t="n">
-        <v>12</v>
+          <t>customer930@example.com</t>
+        </is>
+      </c>
+      <c r="F46" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -3598,26 +4022,26 @@
           <t>EX-10435</t>
         </is>
       </c>
-      <c r="B47" s="45" t="n">
+      <c r="B47" s="53" t="n">
         <v>46291.29166666666</v>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Sample E-book</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>customer654@example.com</t>
-        </is>
-      </c>
-      <c r="F47" s="46" t="n">
-        <v>29</v>
+          <t>customer922@example.com</t>
+        </is>
+      </c>
+      <c r="F47" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
@@ -3631,26 +4055,26 @@
           <t>EX-10434</t>
         </is>
       </c>
-      <c r="B48" s="45" t="n">
+      <c r="B48" s="53" t="n">
         <v>46291</v>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Template Kit (example)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>customer930@example.com</t>
-        </is>
-      </c>
-      <c r="F48" s="46" t="n">
-        <v>29</v>
+          <t>customer464@example.com</t>
+        </is>
+      </c>
+      <c r="F48" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -3664,7 +4088,7 @@
           <t>EX-10433</t>
         </is>
       </c>
-      <c r="B49" s="45" t="n">
+      <c r="B49" s="53" t="n">
         <v>46290.70833333334</v>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -3674,16 +4098,16 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Template Kit (example)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>customer922@example.com</t>
-        </is>
-      </c>
-      <c r="F49" s="46" t="n">
-        <v>19</v>
+          <t>customer365@example.com</t>
+        </is>
+      </c>
+      <c r="F49" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
@@ -3697,30 +4121,30 @@
           <t>EX-10432</t>
         </is>
       </c>
-      <c r="B50" s="45" t="n">
+      <c r="B50" s="53" t="n">
         <v>46290.41666666666</v>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Template Kit (example)</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>customer464@example.com</t>
-        </is>
-      </c>
-      <c r="F50" s="46" t="n">
-        <v>19</v>
+          <t>customer557@example.com</t>
+        </is>
+      </c>
+      <c r="F50" s="54" t="n">
+        <v>12</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>refunded</t>
         </is>
       </c>
     </row>
@@ -3730,7 +4154,7 @@
           <t>EX-10431</t>
         </is>
       </c>
-      <c r="B51" s="45" t="n">
+      <c r="B51" s="53" t="n">
         <v>46290.125</v>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3740,16 +4164,16 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Sample Icon Pack</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>customer583@example.com</t>
-        </is>
-      </c>
-      <c r="F51" s="46" t="n">
-        <v>9</v>
+          <t>customer204@example.com</t>
+        </is>
+      </c>
+      <c r="F51" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
@@ -3763,7 +4187,7 @@
           <t>EX-10430</t>
         </is>
       </c>
-      <c r="B52" s="45" t="n">
+      <c r="B52" s="53" t="n">
         <v>46289.83333333334</v>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -3778,15 +4202,15 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>customer557@example.com</t>
-        </is>
-      </c>
-      <c r="F52" s="46" t="n">
-        <v>19</v>
+          <t>customer309@example.com</t>
+        </is>
+      </c>
+      <c r="F52" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -3796,12 +4220,12 @@
           <t>EX-10429</t>
         </is>
       </c>
-      <c r="B53" s="45" t="n">
+      <c r="B53" s="53" t="n">
         <v>46289.54166666666</v>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -3811,15 +4235,15 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>customer325@example.com</t>
-        </is>
-      </c>
-      <c r="F53" s="46" t="n">
-        <v>29</v>
+          <t>customer590@example.com</t>
+        </is>
+      </c>
+      <c r="F53" s="54" t="n">
+        <v>79</v>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>refunded</t>
         </is>
       </c>
     </row>
@@ -3829,26 +4253,26 @@
           <t>EX-10428</t>
         </is>
       </c>
-      <c r="B54" s="45" t="n">
+      <c r="B54" s="53" t="n">
         <v>46289.25</v>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Sample Icon Pack</t>
+          <t>Sample E-book</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>customer445@example.com</t>
-        </is>
-      </c>
-      <c r="F54" s="46" t="n">
-        <v>19</v>
+          <t>customer222@example.com</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="n">
+        <v>12</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -3862,30 +4286,30 @@
           <t>EX-10427</t>
         </is>
       </c>
-      <c r="B55" s="45" t="n">
+      <c r="B55" s="53" t="n">
         <v>46288.95833333334</v>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Template Kit (example)</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>customer960@example.com</t>
-        </is>
-      </c>
-      <c r="F55" s="46" t="n">
-        <v>49</v>
+          <t>customer282@example.com</t>
+        </is>
+      </c>
+      <c r="F55" s="54" t="n">
+        <v>12</v>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>refunded</t>
+          <t>paid</t>
         </is>
       </c>
     </row>
@@ -3895,26 +4319,26 @@
           <t>EX-10426</t>
         </is>
       </c>
-      <c r="B56" s="45" t="n">
+      <c r="B56" s="53" t="n">
         <v>46288.66666666666</v>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>customer186@example.com</t>
-        </is>
-      </c>
-      <c r="F56" s="46" t="n">
-        <v>49</v>
+          <t>customer920@example.com</t>
+        </is>
+      </c>
+      <c r="F56" s="54" t="n">
+        <v>12</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -3928,12 +4352,12 @@
           <t>EX-10425</t>
         </is>
       </c>
-      <c r="B57" s="45" t="n">
+      <c r="B57" s="53" t="n">
         <v>46288.375</v>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3943,11 +4367,11 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>customer868@example.com</t>
-        </is>
-      </c>
-      <c r="F57" s="46" t="n">
-        <v>9</v>
+          <t>customer186@example.com</t>
+        </is>
+      </c>
+      <c r="F57" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
@@ -3961,26 +4385,26 @@
           <t>EX-10424</t>
         </is>
       </c>
-      <c r="B58" s="45" t="n">
+      <c r="B58" s="53" t="n">
         <v>46288.08333333334</v>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Template Kit (example)</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>customer908@example.com</t>
-        </is>
-      </c>
-      <c r="F58" s="46" t="n">
-        <v>49</v>
+          <t>customer254@example.com</t>
+        </is>
+      </c>
+      <c r="F58" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -3994,26 +4418,26 @@
           <t>EX-10423</t>
         </is>
       </c>
-      <c r="B59" s="45" t="n">
+      <c r="B59" s="53" t="n">
         <v>46287.79166666666</v>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>customer505@example.com</t>
-        </is>
-      </c>
-      <c r="F59" s="46" t="n">
-        <v>29</v>
+          <t>customer946@example.com</t>
+        </is>
+      </c>
+      <c r="F59" s="54" t="n">
+        <v>49</v>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
@@ -4027,25 +4451,25 @@
           <t>EX-10422</t>
         </is>
       </c>
-      <c r="B60" s="45" t="n">
+      <c r="B60" s="53" t="n">
         <v>46287.5</v>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Sample E-book</t>
+          <t>Sample Icon Pack</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>customer262@example.com</t>
-        </is>
-      </c>
-      <c r="F60" s="46" t="n">
+          <t>customer661@example.com</t>
+        </is>
+      </c>
+      <c r="F60" s="54" t="n">
         <v>49</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -4060,25 +4484,25 @@
           <t>EX-10421</t>
         </is>
       </c>
-      <c r="B61" s="45" t="n">
+      <c r="B61" s="53" t="n">
         <v>46287.20833333334</v>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Sample Icon Pack</t>
+          <t>Example Course Bundle</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>customer704@example.com</t>
-        </is>
-      </c>
-      <c r="F61" s="46" t="n">
+          <t>customer918@example.com</t>
+        </is>
+      </c>
+      <c r="F61" s="54" t="n">
         <v>19</v>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -4097,7 +4521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000D0D0D"/>
@@ -4117,37 +4541,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Subscription ID</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="44" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Customer email</t>
         </is>
       </c>
-      <c r="E1" s="44" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Started</t>
         </is>
       </c>
-      <c r="G1" s="44" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>MRR (USD)</t>
         </is>
@@ -4161,7 +4585,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -4171,18 +4595,18 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>customer726@example.com</t>
+          <t>customer544@example.com</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="F2" s="47" t="n">
-        <v>46256</v>
-      </c>
-      <c r="G2" s="46" t="n">
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F2" s="55" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G2" s="54" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4194,17 +4618,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>customer121@example.com</t>
+          <t>customer613@example.com</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -4212,10 +4636,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="47" t="n">
-        <v>46070</v>
-      </c>
-      <c r="G3" s="46" t="n">
+      <c r="F3" s="55" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G3" s="54" t="n">
         <v>29</v>
       </c>
     </row>
@@ -4227,17 +4651,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>customer992@example.com</t>
+          <t>customer162@example.com</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -4245,11 +4669,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F4" s="47" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G4" s="46" t="n">
-        <v>19</v>
+      <c r="F4" s="55" t="n">
+        <v>46256</v>
+      </c>
+      <c r="G4" s="54" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -4260,7 +4684,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -4270,19 +4694,19 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>customer613@example.com</t>
+          <t>customer946@example.com</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F5" s="47" t="n">
-        <v>46182</v>
-      </c>
-      <c r="G5" s="46" t="n">
-        <v>29</v>
+          <t>past_due</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="n">
+        <v>46099</v>
+      </c>
+      <c r="G5" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -4293,7 +4717,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -4303,7 +4727,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>customer162@example.com</t>
+          <t>customer993@example.com</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -4311,11 +4735,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F6" s="47" t="n">
-        <v>46256</v>
-      </c>
-      <c r="G6" s="46" t="n">
-        <v>29</v>
+      <c r="F6" s="55" t="n">
+        <v>46101</v>
+      </c>
+      <c r="G6" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -4326,28 +4750,28 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>customer946@example.com</t>
+          <t>customer244@example.com</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>past_due</t>
-        </is>
-      </c>
-      <c r="F7" s="47" t="n">
-        <v>46099</v>
-      </c>
-      <c r="G7" s="46" t="n">
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="n">
+        <v>46071</v>
+      </c>
+      <c r="G7" s="54" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4364,12 +4788,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>customer993@example.com</t>
+          <t>customer903@example.com</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -4377,10 +4801,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F8" s="47" t="n">
-        <v>46101</v>
-      </c>
-      <c r="G8" s="46" t="n">
+      <c r="F8" s="55" t="n">
+        <v>46267</v>
+      </c>
+      <c r="G8" s="54" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4392,17 +4816,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>customer244@example.com</t>
+          <t>customer143@example.com</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -4410,11 +4834,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F9" s="47" t="n">
-        <v>46071</v>
-      </c>
-      <c r="G9" s="46" t="n">
-        <v>9</v>
+      <c r="F9" s="55" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G9" s="54" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -4425,17 +4849,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>customer903@example.com</t>
+          <t>customer553@example.com</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -4443,11 +4867,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F10" s="47" t="n">
-        <v>46267</v>
-      </c>
-      <c r="G10" s="46" t="n">
-        <v>9</v>
+      <c r="F10" s="55" t="n">
+        <v>46285</v>
+      </c>
+      <c r="G10" s="54" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -4458,7 +4882,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -4468,19 +4892,19 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>customer143@example.com</t>
+          <t>customer563@example.com</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F11" s="47" t="n">
-        <v>46280</v>
-      </c>
-      <c r="G11" s="46" t="n">
-        <v>29</v>
+          <t>past_due</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="n">
+        <v>46291</v>
+      </c>
+      <c r="G11" s="54" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -4491,7 +4915,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -4501,19 +4925,19 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>customer553@example.com</t>
+          <t>customer815@example.com</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F12" s="47" t="n">
-        <v>46285</v>
-      </c>
-      <c r="G12" s="46" t="n">
-        <v>29</v>
+          <t>past_due</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="n">
+        <v>46160</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -4524,28 +4948,28 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>customer563@example.com</t>
+          <t>customer526@example.com</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>past_due</t>
-        </is>
-      </c>
-      <c r="F13" s="47" t="n">
-        <v>46291</v>
-      </c>
-      <c r="G13" s="46" t="n">
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G13" s="54" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4557,7 +4981,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -4567,19 +4991,19 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>customer815@example.com</t>
+          <t>customer538@example.com</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>past_due</t>
-        </is>
-      </c>
-      <c r="F14" s="47" t="n">
-        <v>46160</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>9</v>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="n">
+        <v>46134</v>
+      </c>
+      <c r="G14" s="54" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4590,7 +5014,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -4600,7 +5024,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>customer526@example.com</t>
+          <t>customer833@example.com</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -4608,11 +5032,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F15" s="47" t="n">
-        <v>46218</v>
-      </c>
-      <c r="G15" s="46" t="n">
-        <v>19</v>
+      <c r="F15" s="55" t="n">
+        <v>46090</v>
+      </c>
+      <c r="G15" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -4623,7 +5047,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -4633,7 +5057,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>customer538@example.com</t>
+          <t>customer864@example.com</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -4641,11 +5065,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F16" s="47" t="n">
-        <v>46134</v>
-      </c>
-      <c r="G16" s="46" t="n">
-        <v>19</v>
+      <c r="F16" s="55" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -4656,7 +5080,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -4666,7 +5090,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>customer833@example.com</t>
+          <t>customer823@example.com</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -4674,11 +5098,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F17" s="47" t="n">
-        <v>46090</v>
-      </c>
-      <c r="G17" s="46" t="n">
-        <v>9</v>
+      <c r="F17" s="55" t="n">
+        <v>46278</v>
+      </c>
+      <c r="G17" s="54" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -4689,7 +5113,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -4699,7 +5123,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>customer864@example.com</t>
+          <t>customer465@example.com</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -4707,11 +5131,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F18" s="47" t="n">
-        <v>46219</v>
-      </c>
-      <c r="G18" s="46" t="n">
-        <v>9</v>
+      <c r="F18" s="55" t="n">
+        <v>46077</v>
+      </c>
+      <c r="G18" s="54" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -4722,17 +5146,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>customer265@example.com</t>
+          <t>customer667@example.com</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -4740,11 +5164,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F19" s="47" t="n">
-        <v>46278</v>
-      </c>
-      <c r="G19" s="46" t="n">
-        <v>19</v>
+      <c r="F19" s="55" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G19" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -4755,29 +5179,29 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>customer465@example.com</t>
+          <t>customer629@example.com</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F20" s="47" t="n">
-        <v>46077</v>
-      </c>
-      <c r="G20" s="46" t="n">
-        <v>19</v>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="F20" s="55" t="n">
+        <v>46159</v>
+      </c>
+      <c r="G20" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -4793,12 +5217,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>customer667@example.com</t>
+          <t>customer997@example.com</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -4806,11 +5230,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F21" s="47" t="n">
-        <v>46257</v>
-      </c>
-      <c r="G21" s="46" t="n">
-        <v>9</v>
+      <c r="F21" s="55" t="n">
+        <v>46062</v>
+      </c>
+      <c r="G21" s="54" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -4821,29 +5245,29 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Lemon Squeezy</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>customer629@example.com</t>
+          <t>customer376@example.com</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="F22" s="47" t="n">
-        <v>46159</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>9</v>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F22" s="55" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G22" s="54" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -4854,28 +5278,28 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>customer997@example.com</t>
+          <t>customer252@example.com</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F23" s="47" t="n">
-        <v>46062</v>
-      </c>
-      <c r="G23" s="46" t="n">
+          <t>past_due</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="n">
+        <v>46284</v>
+      </c>
+      <c r="G23" s="54" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4887,7 +5311,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4897,7 +5321,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>customer376@example.com</t>
+          <t>customer385@example.com</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -4905,11 +5329,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F24" s="47" t="n">
-        <v>46231</v>
-      </c>
-      <c r="G24" s="46" t="n">
-        <v>29</v>
+      <c r="F24" s="55" t="n">
+        <v>46095</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -4920,29 +5344,29 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>customer252@example.com</t>
+          <t>customer749@example.com</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>past_due</t>
-        </is>
-      </c>
-      <c r="F25" s="47" t="n">
-        <v>46284</v>
-      </c>
-      <c r="G25" s="46" t="n">
-        <v>19</v>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="n">
+        <v>46145</v>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -4953,17 +5377,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Team</t>
+          <t>Demo SaaS · Pro</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>customer191@example.com</t>
+          <t>customer370@example.com</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -4971,11 +5395,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F26" s="47" t="n">
-        <v>46048</v>
-      </c>
-      <c r="G26" s="46" t="n">
-        <v>29</v>
+      <c r="F26" s="55" t="n">
+        <v>46235</v>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -4986,7 +5410,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>CSV import</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4996,19 +5420,19 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>customer174@example.com</t>
+          <t>customer374@example.com</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F27" s="47" t="n">
-        <v>46043</v>
-      </c>
-      <c r="G27" s="46" t="n">
-        <v>9</v>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="n">
+        <v>46083</v>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="28">
@@ -5029,7 +5453,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>customer722@example.com</t>
+          <t>customer265@example.com</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -5037,10 +5461,10 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F28" s="47" t="n">
-        <v>46062</v>
-      </c>
-      <c r="G28" s="46" t="n">
+      <c r="F28" s="55" t="n">
+        <v>46028</v>
+      </c>
+      <c r="G28" s="54" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5052,28 +5476,28 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
+          <t>Gumroad</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>customer447@example.com</t>
+          <t>customer643@example.com</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>past_due</t>
-        </is>
-      </c>
-      <c r="F29" s="47" t="n">
-        <v>46212</v>
-      </c>
-      <c r="G29" s="46" t="n">
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F29" s="55" t="n">
+        <v>46157</v>
+      </c>
+      <c r="G29" s="54" t="n">
         <v>29</v>
       </c>
     </row>
@@ -5085,17 +5509,17 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
+          <t>Polar</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Demo SaaS · Pro</t>
+          <t>Demo SaaS · Team</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>customer639@example.com</t>
+          <t>customer455@example.com</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -5103,11 +5527,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F30" s="47" t="n">
-        <v>46059</v>
-      </c>
-      <c r="G30" s="46" t="n">
-        <v>19</v>
+      <c r="F30" s="55" t="n">
+        <v>46144</v>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -5128,7 +5552,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>customer306@example.com</t>
+          <t>customer626@example.com</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -5136,16 +5560,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F31" s="47" t="n">
-        <v>46159</v>
-      </c>
-      <c r="G31" s="46" t="n">
+      <c r="F31" s="55" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G31" s="54" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E31">
-    <cfRule type="expression" priority="1" dxfId="2">
+    <cfRule type="expression" priority="1" dxfId="8">
       <formula>E2="past_due"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5153,7 +5577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000D0D0D"/>
@@ -5172,32 +5596,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Customer email</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>First source</t>
         </is>
       </c>
-      <c r="C1" s="44" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>First purchase</t>
         </is>
       </c>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Last purchase</t>
         </is>
       </c>
-      <c r="E1" s="44" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Lifetime revenue (USD)</t>
         </is>
@@ -5211,20 +5635,20 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
-        </is>
-      </c>
-      <c r="C2" s="47" t="n">
-        <v>45886</v>
-      </c>
-      <c r="D2" s="47" t="n">
-        <v>46298</v>
-      </c>
-      <c r="E2" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="46" t="n">
-        <v>364</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C2" s="55" t="n">
+        <v>45977</v>
+      </c>
+      <c r="D2" s="55" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E2" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="54" t="n">
+        <v>324</v>
       </c>
     </row>
     <row r="3">
@@ -5235,20 +5659,20 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C3" s="47" t="n">
-        <v>45779</v>
-      </c>
-      <c r="D3" s="47" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E3" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" s="46" t="n">
-        <v>573</v>
+          <t>Polar</t>
+        </is>
+      </c>
+      <c r="C3" s="55" t="n">
+        <v>45758</v>
+      </c>
+      <c r="D3" s="55" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E3" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="54" t="n">
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -5262,17 +5686,17 @@
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="C4" s="47" t="n">
-        <v>45916</v>
-      </c>
-      <c r="D4" s="47" t="n">
-        <v>46242</v>
-      </c>
-      <c r="E4" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="46" t="n">
-        <v>451</v>
+      <c r="C4" s="55" t="n">
+        <v>45717</v>
+      </c>
+      <c r="D4" s="55" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E4" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="54" t="n">
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -5283,20 +5707,20 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
-        </is>
-      </c>
-      <c r="C5" s="47" t="n">
-        <v>45887</v>
-      </c>
-      <c r="D5" s="47" t="n">
+          <t>Lemon Squeezy</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="n">
+        <v>45710</v>
+      </c>
+      <c r="D5" s="55" t="n">
         <v>46274</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="46" t="n">
-        <v>229</v>
+      <c r="F5" s="54" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="6">
@@ -5307,20 +5731,20 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C6" s="47" t="n">
-        <v>45815</v>
-      </c>
-      <c r="D6" s="47" t="n">
-        <v>46298</v>
-      </c>
-      <c r="E6" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="46" t="n">
-        <v>364</v>
+          <t>Gumroad</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="n">
+        <v>45672</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="54" t="n">
+        <v>465</v>
       </c>
     </row>
     <row r="7">
@@ -5334,17 +5758,17 @@
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="C7" s="47" t="n">
-        <v>45717</v>
-      </c>
-      <c r="D7" s="47" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E7" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="46" t="n">
-        <v>176</v>
+      <c r="C7" s="55" t="n">
+        <v>45789</v>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E7" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="54" t="n">
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -5358,17 +5782,17 @@
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="C8" s="47" t="n">
-        <v>45710</v>
-      </c>
-      <c r="D8" s="47" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E8" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="46" t="n">
-        <v>257</v>
+      <c r="C8" s="55" t="n">
+        <v>45784</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="54" t="n">
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5379,20 +5803,20 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
-        </is>
-      </c>
-      <c r="C9" s="47" t="n">
-        <v>45779</v>
-      </c>
-      <c r="D9" s="47" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E9" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="46" t="n">
-        <v>284</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="n">
+        <v>45704</v>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E9" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="54" t="n">
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -5403,20 +5827,20 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="n">
-        <v>45666</v>
-      </c>
-      <c r="D10" s="47" t="n">
-        <v>46271</v>
-      </c>
-      <c r="E10" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <v>340</v>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="n">
+        <v>45660</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="54" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="11">
@@ -5427,20 +5851,20 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C11" s="47" t="n">
-        <v>45667</v>
-      </c>
-      <c r="D11" s="47" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E11" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="46" t="n">
-        <v>10</v>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="n">
+        <v>45670</v>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E11" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="54" t="n">
+        <v>247</v>
       </c>
     </row>
     <row r="12">
@@ -5451,20 +5875,20 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
-        </is>
-      </c>
-      <c r="C12" s="47" t="n">
-        <v>45841</v>
-      </c>
-      <c r="D12" s="47" t="n">
-        <v>46270</v>
-      </c>
-      <c r="E12" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="46" t="n">
-        <v>214</v>
+          <t>Lemon Squeezy</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="n">
+        <v>45947</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E12" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="54" t="n">
+        <v>515</v>
       </c>
     </row>
     <row r="13">
@@ -5475,20 +5899,20 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C13" s="47" t="n">
-        <v>45925</v>
-      </c>
-      <c r="D13" s="47" t="n">
-        <v>46236</v>
-      </c>
-      <c r="E13" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="46" t="n">
-        <v>100</v>
+          <t>Polar</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="n">
+        <v>45801</v>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>46298</v>
+      </c>
+      <c r="E13" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="54" t="n">
+        <v>534</v>
       </c>
     </row>
     <row r="14">
@@ -5499,20 +5923,20 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C14" s="47" t="n">
-        <v>45857</v>
-      </c>
-      <c r="D14" s="47" t="n">
-        <v>46241</v>
-      </c>
-      <c r="E14" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <v>315</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="n">
+        <v>46014</v>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>46298</v>
+      </c>
+      <c r="E14" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="54" t="n">
+        <v>525</v>
       </c>
     </row>
     <row r="15">
@@ -5523,20 +5947,20 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
-        </is>
-      </c>
-      <c r="C15" s="47" t="n">
-        <v>45969</v>
-      </c>
-      <c r="D15" s="47" t="n">
-        <v>46243</v>
-      </c>
-      <c r="E15" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="46" t="n">
-        <v>407</v>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="n">
+        <v>45684</v>
+      </c>
+      <c r="D15" s="55" t="n">
+        <v>46299</v>
+      </c>
+      <c r="E15" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="54" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -5547,20 +5971,20 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
-        </is>
-      </c>
-      <c r="C16" s="47" t="n">
-        <v>46007</v>
-      </c>
-      <c r="D16" s="47" t="n">
-        <v>46239</v>
-      </c>
-      <c r="E16" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="46" t="n">
-        <v>53</v>
+          <t>Lemon Squeezy</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="n">
+        <v>45737</v>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E16" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="54" t="n">
+        <v>471</v>
       </c>
     </row>
     <row r="17">
@@ -5571,20 +5995,20 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
-        </is>
-      </c>
-      <c r="C17" s="47" t="n">
-        <v>45921</v>
-      </c>
-      <c r="D17" s="47" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E17" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="46" t="n">
-        <v>545</v>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="n">
+        <v>45678</v>
+      </c>
+      <c r="D17" s="55" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E17" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="54" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="18">
@@ -5598,17 +6022,17 @@
           <t>Gumroad</t>
         </is>
       </c>
-      <c r="C18" s="47" t="n">
-        <v>45957</v>
-      </c>
-      <c r="D18" s="47" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E18" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="46" t="n">
-        <v>40</v>
+      <c r="C18" s="55" t="n">
+        <v>45672</v>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E18" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="54" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="19">
@@ -5619,20 +6043,20 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C19" s="47" t="n">
-        <v>45737</v>
-      </c>
-      <c r="D19" s="47" t="n">
-        <v>46267</v>
-      </c>
-      <c r="E19" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="46" t="n">
-        <v>471</v>
+          <t>CSV import</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="n">
+        <v>45712</v>
+      </c>
+      <c r="D19" s="55" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E19" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="54" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -5646,17 +6070,17 @@
           <t>Gumroad</t>
         </is>
       </c>
-      <c r="C20" s="47" t="n">
-        <v>45678</v>
-      </c>
-      <c r="D20" s="47" t="n">
-        <v>46243</v>
-      </c>
-      <c r="E20" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="46" t="n">
-        <v>510</v>
+      <c r="C20" s="55" t="n">
+        <v>45771</v>
+      </c>
+      <c r="D20" s="55" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E20" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="54" t="n">
+        <v>514</v>
       </c>
     </row>
     <row r="21">
@@ -5667,20 +6091,20 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Polar</t>
-        </is>
-      </c>
-      <c r="C21" s="47" t="n">
-        <v>45672</v>
-      </c>
-      <c r="D21" s="47" t="n">
-        <v>46243</v>
-      </c>
-      <c r="E21" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="46" t="n">
-        <v>103</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="n">
+        <v>45704</v>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E21" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="54" t="n">
+        <v>212</v>
       </c>
     </row>
     <row r="22">
@@ -5691,20 +6115,20 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="n">
-        <v>45903</v>
-      </c>
-      <c r="D22" s="47" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E22" s="48" t="n">
+          <t>Lemon Squeezy</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="n">
+        <v>45935</v>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>46270</v>
+      </c>
+      <c r="E22" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="46" t="n">
-        <v>85</v>
+      <c r="F22" s="54" t="n">
+        <v>590</v>
       </c>
     </row>
     <row r="23">
@@ -5718,17 +6142,17 @@
           <t>Polar</t>
         </is>
       </c>
-      <c r="C23" s="47" t="n">
-        <v>45771</v>
-      </c>
-      <c r="D23" s="47" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E23" s="48" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="46" t="n">
-        <v>514</v>
+      <c r="C23" s="55" t="n">
+        <v>45673</v>
+      </c>
+      <c r="D23" s="55" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E23" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="54" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -5742,17 +6166,17 @@
           <t>Polar</t>
         </is>
       </c>
-      <c r="C24" s="47" t="n">
-        <v>45704</v>
-      </c>
-      <c r="D24" s="47" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E24" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="46" t="n">
-        <v>212</v>
+      <c r="C24" s="55" t="n">
+        <v>45977</v>
+      </c>
+      <c r="D24" s="55" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E24" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="54" t="n">
+        <v>484</v>
       </c>
     </row>
     <row r="25">
@@ -5763,20 +6187,20 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="C25" s="47" t="n">
-        <v>45935</v>
-      </c>
-      <c r="D25" s="47" t="n">
-        <v>46270</v>
-      </c>
-      <c r="E25" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="46" t="n">
-        <v>590</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="n">
+        <v>45894</v>
+      </c>
+      <c r="D25" s="55" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E25" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="54" t="n">
+        <v>328</v>
       </c>
     </row>
     <row r="26">
@@ -5790,17 +6214,17 @@
           <t>Lemon Squeezy</t>
         </is>
       </c>
-      <c r="C26" s="47" t="n">
-        <v>45673</v>
-      </c>
-      <c r="D26" s="47" t="n">
-        <v>46242</v>
-      </c>
-      <c r="E26" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" s="46" t="n">
-        <v>110</v>
+      <c r="C26" s="55" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D26" s="55" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E26" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="54" t="n">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -5808,7 +6232,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B42318"/>
@@ -5827,32 +6251,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Refund ID</t>
         </is>
       </c>
-      <c r="B1" s="44" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Order ID</t>
         </is>
       </c>
-      <c r="C1" s="44" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="E1" s="44" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Amount (USD)</t>
         </is>
       </c>
-      <c r="F1" s="44" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -5871,18 +6295,18 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
-        </is>
-      </c>
-      <c r="D2" s="47" t="n">
-        <v>46299</v>
-      </c>
-      <c r="E2" s="46" t="n">
-        <v>29</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D2" s="55" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E2" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Requested by customer</t>
         </is>
       </c>
     </row>
@@ -5902,15 +6326,15 @@
           <t>Polar</t>
         </is>
       </c>
-      <c r="D3" s="47" t="n">
-        <v>46304</v>
-      </c>
-      <c r="E3" s="46" t="n">
-        <v>19</v>
+      <c r="D3" s="55" t="n">
+        <v>46297</v>
+      </c>
+      <c r="E3" s="54" t="n">
+        <v>29</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Requested by customer</t>
         </is>
       </c>
     </row>
@@ -5930,15 +6354,15 @@
           <t>Polar</t>
         </is>
       </c>
-      <c r="D4" s="47" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E4" s="46" t="n">
-        <v>9</v>
+      <c r="D4" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E4" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -5955,18 +6379,18 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="D5" s="47" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E5" s="46" t="n">
-        <v>9</v>
+          <t>Polar</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E5" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Requested by customer</t>
         </is>
       </c>
     </row>
@@ -5983,18 +6407,18 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="D6" s="47" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E6" s="46" t="n">
+          <t>Gumroad</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>46299</v>
+      </c>
+      <c r="E6" s="54" t="n">
         <v>19</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Requested by customer</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -6011,18 +6435,18 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Gumroad</t>
-        </is>
-      </c>
-      <c r="D7" s="47" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E7" s="46" t="n">
-        <v>19</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E7" s="54" t="n">
+        <v>9</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Requested by customer</t>
         </is>
       </c>
     </row>
@@ -6039,18 +6463,18 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="n">
-        <v>46299</v>
-      </c>
-      <c r="E8" s="46" t="n">
-        <v>9</v>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E8" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -6067,18 +6491,18 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Lemon Squeezy</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="n">
-        <v>46298</v>
-      </c>
-      <c r="E9" s="46" t="n">
-        <v>29</v>
+          <t>Polar</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E9" s="54" t="n">
+        <v>19</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Chargeback</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008C8C8C"/>
@@ -6102,12 +6526,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -6119,7 +6543,7 @@
           <t>Last sync</t>
         </is>
       </c>
-      <c r="B2" s="50" t="n">
+      <c r="B2" s="58" t="n">
         <v>46304.41805555556</v>
       </c>
     </row>
@@ -6155,7 +6579,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lemon Squeezy, Polar, Gumroad</t>
+          <t>Stripe, Lemon Squeezy, Polar, Gumroad, CSV import</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6591,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Example data — not real customers</t>
+          <t>Example data, not real customers</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008C8C8C"/>
@@ -6219,255 +6643,255 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="n">
+      <c r="A2" s="59" t="n">
         <v>45962</v>
       </c>
-      <c r="B2" s="52" t="n">
+      <c r="B2" s="60" t="n">
         <v>901</v>
       </c>
-      <c r="C2" s="52" t="n">
+      <c r="C2" s="60" t="n">
         <v>272</v>
       </c>
-      <c r="D2" s="52" t="n">
+      <c r="D2" s="60" t="n">
         <v>495</v>
       </c>
-      <c r="E2" s="52">
+      <c r="E2" s="60">
         <f>SUM(B2:D2)</f>
         <v/>
       </c>
-      <c r="F2" s="53" t="n">
+      <c r="F2" s="61" t="n">
         <v>0.034</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="n">
+      <c r="A3" s="59" t="n">
         <v>45992</v>
       </c>
-      <c r="B3" s="52" t="n">
+      <c r="B3" s="60" t="n">
         <v>974</v>
       </c>
-      <c r="C3" s="52" t="n">
+      <c r="C3" s="60" t="n">
         <v>405</v>
       </c>
-      <c r="D3" s="52" t="n">
+      <c r="D3" s="60" t="n">
         <v>548</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="60">
         <f>SUM(B3:D3)</f>
         <v/>
       </c>
-      <c r="F3" s="53" t="n">
+      <c r="F3" s="61" t="n">
         <v>0.031</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="n">
+      <c r="A4" s="59" t="n">
         <v>46023</v>
       </c>
-      <c r="B4" s="52" t="n">
+      <c r="B4" s="60" t="n">
         <v>1100</v>
       </c>
-      <c r="C4" s="52" t="n">
+      <c r="C4" s="60" t="n">
         <v>557</v>
       </c>
-      <c r="D4" s="52" t="n">
+      <c r="D4" s="60" t="n">
         <v>640</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="60">
         <f>SUM(B4:D4)</f>
         <v/>
       </c>
-      <c r="F4" s="53" t="n">
+      <c r="F4" s="61" t="n">
         <v>0.036</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="n">
+      <c r="A5" s="59" t="n">
         <v>46054</v>
       </c>
-      <c r="B5" s="52" t="n">
+      <c r="B5" s="60" t="n">
         <v>1151</v>
       </c>
-      <c r="C5" s="52" t="n">
+      <c r="C5" s="60" t="n">
         <v>686</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="60" t="n">
         <v>680</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="60">
         <f>SUM(B5:D5)</f>
         <v/>
       </c>
-      <c r="F5" s="53" t="n">
+      <c r="F5" s="61" t="n">
         <v>0.028</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="n">
+      <c r="A6" s="59" t="n">
         <v>46082</v>
       </c>
-      <c r="B6" s="52" t="n">
+      <c r="B6" s="60" t="n">
         <v>1249</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="60" t="n">
         <v>794</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="60" t="n">
         <v>714</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="60">
         <f>SUM(B6:D6)</f>
         <v/>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="61" t="n">
         <v>0.026</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="59" t="n">
         <v>46113</v>
       </c>
-      <c r="B7" s="52" t="n">
+      <c r="B7" s="60" t="n">
         <v>1403</v>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="60" t="n">
         <v>935</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="60" t="n">
         <v>687</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="60">
         <f>SUM(B7:D7)</f>
         <v/>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="61" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="59" t="n">
         <v>46143</v>
       </c>
-      <c r="B8" s="52" t="n">
+      <c r="B8" s="60" t="n">
         <v>1442</v>
       </c>
-      <c r="C8" s="52" t="n">
+      <c r="C8" s="60" t="n">
         <v>1055</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="60" t="n">
         <v>793</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="60">
         <f>SUM(B8:D8)</f>
         <v/>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="61" t="n">
         <v>0.027</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="59" t="n">
         <v>46174</v>
       </c>
-      <c r="B9" s="52" t="n">
+      <c r="B9" s="60" t="n">
         <v>1571</v>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="60" t="n">
         <v>1215</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="60" t="n">
         <v>834</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="60">
         <f>SUM(B9:D9)</f>
         <v/>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="61" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="59" t="n">
         <v>46204</v>
       </c>
-      <c r="B10" s="52" t="n">
+      <c r="B10" s="60" t="n">
         <v>1694</v>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="60" t="n">
         <v>1337</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="60" t="n">
         <v>850</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="60">
         <f>SUM(B10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="53" t="n">
+      <c r="F10" s="61" t="n">
         <v>0.029</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="59" t="n">
         <v>46235</v>
       </c>
-      <c r="B11" s="52" t="n">
+      <c r="B11" s="60" t="n">
         <v>1722</v>
       </c>
-      <c r="C11" s="52" t="n">
+      <c r="C11" s="60" t="n">
         <v>1443</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="60" t="n">
         <v>846</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="60">
         <f>SUM(B11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="53" t="n">
+      <c r="F11" s="61" t="n">
         <v>0.026</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="59" t="n">
         <v>46266</v>
       </c>
-      <c r="B12" s="52" t="n">
+      <c r="B12" s="60" t="n">
         <v>1874</v>
       </c>
-      <c r="C12" s="52" t="n">
+      <c r="C12" s="60" t="n">
         <v>1622</v>
       </c>
-      <c r="D12" s="52" t="n">
+      <c r="D12" s="60" t="n">
         <v>908</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="60">
         <f>SUM(B12:D12)</f>
         <v/>
       </c>
-      <c r="F12" s="53" t="n">
-        <v>0.026</v>
+      <c r="F12" s="61" t="n">
+        <v>0.029</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="n">
+      <c r="A13" s="59" t="n">
         <v>46296</v>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="60" t="n">
         <v>1932</v>
       </c>
-      <c r="C13" s="52" t="n">
+      <c r="C13" s="60" t="n">
         <v>1736</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="60" t="n">
         <v>925</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="60">
         <f>SUM(B13:D13)</f>
         <v/>
       </c>
-      <c r="F13" s="53" t="n">
-        <v>0.029</v>
+      <c r="F13" s="61" t="n">
+        <v>0.026</v>
       </c>
     </row>
   </sheetData>
